--- a/artfynd/A 53662-2025 artfynd.xlsx
+++ b/artfynd/A 53662-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5466,6 +5466,113 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129996516</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>475314</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6831718</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53662-2025 artfynd.xlsx
+++ b/artfynd/A 53662-2025 artfynd.xlsx
@@ -5471,7 +5471,7 @@
         <v>129996516</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 53662-2025 artfynd.xlsx
+++ b/artfynd/A 53662-2025 artfynd.xlsx
@@ -5471,7 +5471,7 @@
         <v>129996516</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 53662-2025 artfynd.xlsx
+++ b/artfynd/A 53662-2025 artfynd.xlsx
@@ -5471,7 +5471,7 @@
         <v>129996516</v>
       </c>
       <c r="B51" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 53662-2025 artfynd.xlsx
+++ b/artfynd/A 53662-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127296819</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>129996516</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
